--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>75.60939999999999</v>
+        <v>90.084</v>
       </c>
       <c r="E2" t="n">
-        <v>51.2951</v>
+        <v>57.4974</v>
       </c>
       <c r="F2" t="n">
-        <v>24.3143</v>
+        <v>32.5869</v>
       </c>
       <c r="G2" t="n">
-        <v>40.5063</v>
+        <v>45.8065</v>
       </c>
       <c r="H2" t="n">
-        <v>28.2335</v>
+        <v>34.4755</v>
       </c>
       <c r="I2" t="n">
-        <v>12.2727</v>
+        <v>11.331</v>
       </c>
       <c r="J2" t="n">
-        <v>59.9025</v>
+        <v>67.9136</v>
       </c>
       <c r="K2" t="n">
-        <v>40.8164</v>
+        <v>48.9621</v>
       </c>
       <c r="L2" t="n">
-        <v>19.0862</v>
+        <v>18.9514</v>
       </c>
       <c r="M2" t="n">
-        <v>-19.3966</v>
+        <v>-22.1068</v>
       </c>
       <c r="N2" t="n">
-        <v>-12.5829</v>
+        <v>-14.4864</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.8135</v>
+        <v>-7.6203</v>
       </c>
       <c r="P2" t="n">
-        <v>-6.1246</v>
+        <v>-4.3252</v>
       </c>
       <c r="Q2" t="n">
-        <v>-48.0886</v>
+        <v>-55.087</v>
       </c>
       <c r="R2" t="n">
-        <v>41.9641</v>
+        <v>50.7621</v>
       </c>
       <c r="S2" t="n">
-        <v>33.0771</v>
+        <v>37.945</v>
       </c>
       <c r="T2" t="n">
-        <v>24.2475</v>
+        <v>25.4025</v>
       </c>
       <c r="U2" t="n">
-        <v>8.829700000000001</v>
+        <v>12.5419</v>
       </c>
       <c r="V2" t="n">
-        <v>8.1508</v>
+        <v>10.6579</v>
       </c>
       <c r="W2" t="n">
-        <v>15.234</v>
+        <v>19.2682</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.083299999999999</v>
+        <v>-8.610299999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>52.7701</v>
+        <v>53.52</v>
       </c>
       <c r="E3" t="n">
-        <v>42.3578</v>
+        <v>36.8411</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4122</v>
+        <v>16.6792</v>
       </c>
       <c r="G3" t="n">
-        <v>31.5755</v>
+        <v>15.5093</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.746099999999998</v>
+        <v>10.0393</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3216</v>
+        <v>5.469799999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>52.8063</v>
+        <v>29.2054</v>
       </c>
       <c r="K3" t="n">
-        <v>8.9596</v>
+        <v>16.731</v>
       </c>
       <c r="L3" t="n">
-        <v>43.8472</v>
+        <v>12.4742</v>
       </c>
       <c r="M3" t="n">
-        <v>-21.2309</v>
+        <v>-13.6963</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.7056</v>
+        <v>-6.6917</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.525399999999999</v>
+        <v>-7.004300000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1341</v>
+        <v>17.5276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-35.8397</v>
+        <v>-18.6662</v>
       </c>
       <c r="R3" t="n">
-        <v>34.7057</v>
+        <v>36.1935</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.044899999999999</v>
+        <v>32.1071</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.010899999999999</v>
+        <v>26.2421</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.0336</v>
+        <v>5.8656</v>
       </c>
       <c r="V3" t="n">
-        <v>29.3738</v>
+        <v>-11.6239</v>
       </c>
       <c r="W3" t="n">
-        <v>30.4022</v>
+        <v>0.05979999999999969</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0285</v>
+        <v>-11.6838</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>38.0131</v>
+        <v>51.917</v>
       </c>
       <c r="E4" t="n">
-        <v>26.8231</v>
+        <v>37.0788</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1899</v>
+        <v>14.8382</v>
       </c>
       <c r="G4" t="n">
-        <v>32.2936</v>
+        <v>32.8167</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6916000000000004</v>
+        <v>-1.325300000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>31.6022</v>
+        <v>34.1421</v>
       </c>
       <c r="J4" t="n">
-        <v>36.4183</v>
+        <v>53.9205</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6755</v>
+        <v>14.3035</v>
       </c>
       <c r="L4" t="n">
-        <v>28.743</v>
+        <v>39.6167</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.1245</v>
+        <v>-21.1035</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.9839</v>
+        <v>-15.6289</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8592</v>
+        <v>-5.4747</v>
       </c>
       <c r="P4" t="n">
-        <v>-13.6101</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q4" t="n">
-        <v>-46.0474</v>
+        <v>-42.7948</v>
       </c>
       <c r="R4" t="n">
-        <v>32.437</v>
+        <v>40.5188</v>
       </c>
       <c r="S4" t="n">
-        <v>8.6915</v>
+        <v>-8.9855</v>
       </c>
       <c r="T4" t="n">
-        <v>12.6695</v>
+        <v>-6.674399999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.9779</v>
+        <v>-2.3114</v>
       </c>
       <c r="V4" t="n">
-        <v>10.6378</v>
+        <v>30.3622</v>
       </c>
       <c r="W4" t="n">
-        <v>23.7823</v>
+        <v>32.6275</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.1445</v>
+        <v>-2.2654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>33.7763</v>
+        <v>42.927</v>
       </c>
       <c r="E5" t="n">
-        <v>22.8189</v>
+        <v>34.689</v>
       </c>
       <c r="F5" t="n">
-        <v>10.9573</v>
+        <v>8.237800000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>5.675199999999999</v>
+        <v>31.0144</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6969</v>
+        <v>2.0785</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9783</v>
+        <v>28.9356</v>
       </c>
       <c r="J5" t="n">
-        <v>20.1107</v>
+        <v>45.1506</v>
       </c>
       <c r="K5" t="n">
-        <v>8.691800000000001</v>
+        <v>11.7912</v>
       </c>
       <c r="L5" t="n">
-        <v>11.419</v>
+        <v>33.3597</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.4353</v>
+        <v>-14.1366</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.994899999999999</v>
+        <v>-9.712400000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.4409</v>
+        <v>-4.4239</v>
       </c>
       <c r="P5" t="n">
-        <v>13.3829</v>
+        <v>-11.3815</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.4664</v>
+        <v>-54.6319</v>
       </c>
       <c r="R5" t="n">
-        <v>30.8492</v>
+        <v>43.2501</v>
       </c>
       <c r="S5" t="n">
-        <v>26.3191</v>
+        <v>9.116</v>
       </c>
       <c r="T5" t="n">
-        <v>21.2984</v>
+        <v>11.4556</v>
       </c>
       <c r="U5" t="n">
-        <v>5.020700000000001</v>
+        <v>-2.3398</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.6011</v>
+        <v>14.178</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.124</v>
+        <v>32.7142</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.477</v>
+        <v>-18.5359</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>31.3849</v>
+        <v>38.7805</v>
       </c>
       <c r="E6" t="n">
-        <v>17.9238</v>
+        <v>24.9203</v>
       </c>
       <c r="F6" t="n">
-        <v>13.4611</v>
+        <v>13.86</v>
       </c>
       <c r="G6" t="n">
-        <v>9.4413</v>
+        <v>9.5379</v>
       </c>
       <c r="H6" t="n">
-        <v>8.2583</v>
+        <v>9.8659</v>
       </c>
       <c r="I6" t="n">
-        <v>1.183000000000001</v>
+        <v>-0.3282000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>19.8084</v>
+        <v>24.6113</v>
       </c>
       <c r="K6" t="n">
-        <v>12.5685</v>
+        <v>16.0019</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2401</v>
+        <v>8.609500000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.3673</v>
+        <v>-15.0734</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.3098</v>
+        <v>-6.1358</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.056999999999999</v>
+        <v>-8.9376</v>
       </c>
       <c r="P6" t="n">
-        <v>17.6929</v>
+        <v>21.8527</v>
       </c>
       <c r="Q6" t="n">
-        <v>-15.6517</v>
+        <v>-19.3491</v>
       </c>
       <c r="R6" t="n">
-        <v>33.3445</v>
+        <v>41.2017</v>
       </c>
       <c r="S6" t="n">
-        <v>18.5835</v>
+        <v>25.209</v>
       </c>
       <c r="T6" t="n">
-        <v>12.352</v>
+        <v>17.0473</v>
       </c>
       <c r="U6" t="n">
-        <v>6.2317</v>
+        <v>8.161300000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-14.333</v>
+        <v>-17.8185</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4146</v>
+        <v>2.6108</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.7479</v>
+        <v>-20.4293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>24.9414</v>
+        <v>28.8635</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4269</v>
+        <v>27.5724</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5149000000000001</v>
+        <v>1.2912</v>
       </c>
       <c r="G7" t="n">
-        <v>23.2269</v>
+        <v>33.8445</v>
       </c>
       <c r="H7" t="n">
-        <v>12.9066</v>
+        <v>12.1535</v>
       </c>
       <c r="I7" t="n">
-        <v>10.3205</v>
+        <v>21.6906</v>
       </c>
       <c r="J7" t="n">
-        <v>36.1268</v>
+        <v>54.5956</v>
       </c>
       <c r="K7" t="n">
-        <v>16.4496</v>
+        <v>24.1242</v>
       </c>
       <c r="L7" t="n">
-        <v>19.6774</v>
+        <v>30.472</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.8997</v>
+        <v>-20.7515</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.5433</v>
+        <v>-11.9703</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.357000000000001</v>
+        <v>-8.781000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3098</v>
+        <v>-2.2761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.3542</v>
+        <v>-44.3884</v>
       </c>
       <c r="R7" t="n">
-        <v>32.664</v>
+        <v>42.1121</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.3143</v>
+        <v>-5.0898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6173999999999999</v>
+        <v>-2.3471</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.9315</v>
+        <v>-2.7428</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7189</v>
+        <v>2.3856</v>
       </c>
       <c r="W7" t="n">
-        <v>16.0369</v>
+        <v>19.7118</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.3181</v>
+        <v>-17.3262</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>24.0595</v>
+        <v>24.1084</v>
       </c>
       <c r="E8" t="n">
-        <v>3.535299999999999</v>
+        <v>3.2023</v>
       </c>
       <c r="F8" t="n">
-        <v>20.5243</v>
+        <v>20.906</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.381699999999999</v>
+        <v>-9.3499</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9603</v>
+        <v>-3.9197</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.4219</v>
+        <v>-5.4299</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.393699999999999</v>
+        <v>-4.656199999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3297</v>
+        <v>-1.455</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.0639</v>
+        <v>-3.201300000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.9882</v>
+        <v>-4.6937</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.6304</v>
+        <v>-2.4647</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.358099999999999</v>
+        <v>-2.2284</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4954</v>
+        <v>2.5042</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.415</v>
+        <v>-20.487</v>
       </c>
       <c r="R8" t="n">
-        <v>22.9102</v>
+        <v>22.991</v>
       </c>
       <c r="S8" t="n">
-        <v>17.1915</v>
+        <v>17.2495</v>
       </c>
       <c r="T8" t="n">
-        <v>10.6038</v>
+        <v>10.6697</v>
       </c>
       <c r="U8" t="n">
-        <v>6.5875</v>
+        <v>6.579400000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>13.755</v>
+        <v>13.7048</v>
       </c>
       <c r="W8" t="n">
-        <v>17.7398</v>
+        <v>17.6756</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.985</v>
+        <v>-3.970899999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>21.2249</v>
+        <v>20.3726</v>
       </c>
       <c r="E9" t="n">
-        <v>23.2014</v>
+        <v>6.481199999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9765</v>
+        <v>13.8912</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3049</v>
+        <v>33.0059</v>
       </c>
       <c r="H9" t="n">
-        <v>8.710800000000001</v>
+        <v>17.9709</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.4058</v>
+        <v>15.0358</v>
       </c>
       <c r="J9" t="n">
-        <v>16.1446</v>
+        <v>47.2525</v>
       </c>
       <c r="K9" t="n">
-        <v>15.7174</v>
+        <v>28.4582</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4273000000000002</v>
+        <v>18.7949</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.8398</v>
+        <v>-14.2467</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.0064</v>
+        <v>-10.4877</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.8331</v>
+        <v>-3.7589</v>
       </c>
       <c r="P9" t="n">
-        <v>14.971</v>
+        <v>-7.284400000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.2394</v>
+        <v>-46.8923</v>
       </c>
       <c r="R9" t="n">
-        <v>32.2105</v>
+        <v>39.6082</v>
       </c>
       <c r="S9" t="n">
-        <v>2.507499999999999</v>
+        <v>0.4511999999999997</v>
       </c>
       <c r="T9" t="n">
-        <v>7.8733</v>
+        <v>-2.7677</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.3655</v>
+        <v>3.219</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5588999999999991</v>
+        <v>-5.8003</v>
       </c>
       <c r="W9" t="n">
-        <v>16.423</v>
+        <v>8.888400000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.982</v>
+        <v>-14.6887</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>15.9105</v>
+        <v>20.3436</v>
       </c>
       <c r="E10" t="n">
-        <v>15.8802</v>
+        <v>23.4898</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03080000000000083</v>
+        <v>-3.146</v>
       </c>
       <c r="G10" t="n">
-        <v>22.4488</v>
+        <v>19.104</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8796</v>
+        <v>11.4071</v>
       </c>
       <c r="I10" t="n">
-        <v>16.5693</v>
+        <v>7.696999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>36.6072</v>
+        <v>35.3609</v>
       </c>
       <c r="K10" t="n">
-        <v>14.2395</v>
+        <v>16.6968</v>
       </c>
       <c r="L10" t="n">
-        <v>22.3673</v>
+        <v>18.6645</v>
       </c>
       <c r="M10" t="n">
-        <v>-14.1582</v>
+        <v>-16.2568</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.3599</v>
+        <v>-5.2895</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.7982</v>
+        <v>-10.9674</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2681</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-35.1592</v>
+        <v>-29.8197</v>
       </c>
       <c r="R10" t="n">
-        <v>32.8909</v>
+        <v>36.6489</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.4818</v>
+        <v>-6.3409</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9263</v>
+        <v>0.3442999999999998</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5556</v>
+        <v>-6.6852</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2119999999999999</v>
+        <v>0.7512999999999996</v>
       </c>
       <c r="W10" t="n">
-        <v>16.3583</v>
+        <v>17.6043</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.1462</v>
+        <v>-16.8529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>13.0631</v>
+        <v>20.1007</v>
       </c>
       <c r="E11" t="n">
-        <v>7.1717</v>
+        <v>24.7805</v>
       </c>
       <c r="F11" t="n">
-        <v>5.891400000000001</v>
+        <v>-4.6797</v>
       </c>
       <c r="G11" t="n">
-        <v>20.6672</v>
+        <v>5.2288</v>
       </c>
       <c r="H11" t="n">
-        <v>10.466</v>
+        <v>10.0594</v>
       </c>
       <c r="I11" t="n">
-        <v>10.2011</v>
+        <v>-4.8303</v>
       </c>
       <c r="J11" t="n">
-        <v>35.0519</v>
+        <v>21.0494</v>
       </c>
       <c r="K11" t="n">
-        <v>18.8334</v>
+        <v>19.7736</v>
       </c>
       <c r="L11" t="n">
-        <v>16.2178</v>
+        <v>1.2758</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.3844</v>
+        <v>-15.8204</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.3675</v>
+        <v>-9.7143</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.0167</v>
+        <v>-6.106299999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1343</v>
+        <v>15.7067</v>
       </c>
       <c r="Q11" t="n">
-        <v>-30.3958</v>
+        <v>-21.1699</v>
       </c>
       <c r="R11" t="n">
-        <v>29.2615</v>
+        <v>36.8768</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6005</v>
+        <v>-0.181</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.1655</v>
+        <v>5.862000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5648</v>
+        <v>-6.0428</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8693</v>
+        <v>-0.6536999999999997</v>
       </c>
       <c r="W11" t="n">
-        <v>7.681100000000001</v>
+        <v>19.039</v>
       </c>
       <c r="X11" t="n">
-        <v>-11.5504</v>
+        <v>-19.6927</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9683</v>
+        <v>3.601300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8487</v>
+        <v>-1.484300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>8.8171</v>
+        <v>5.0855</v>
       </c>
       <c r="G12" t="n">
-        <v>7.165699999999999</v>
+        <v>-7.2277</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5755999999999997</v>
+        <v>-5.1522</v>
       </c>
       <c r="I12" t="n">
-        <v>7.741300000000001</v>
+        <v>-2.0754</v>
       </c>
       <c r="J12" t="n">
-        <v>11.512</v>
+        <v>1.8123</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7955</v>
+        <v>5.1184</v>
       </c>
       <c r="L12" t="n">
-        <v>6.716299999999999</v>
+        <v>-3.306500000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.3459</v>
+        <v>-9.040099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.3708</v>
+        <v>-10.2709</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0248</v>
+        <v>1.231</v>
       </c>
       <c r="P12" t="n">
-        <v>6.3514</v>
+        <v>14.1132</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.9711</v>
+        <v>-16.1622</v>
       </c>
       <c r="R12" t="n">
-        <v>21.3222</v>
+        <v>30.2753</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3178</v>
+        <v>6.5215</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0293</v>
+        <v>6.313800000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7113000000000002</v>
+        <v>0.2075999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.2308</v>
+        <v>-9.8055</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6396</v>
+        <v>6.5518</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.870200000000001</v>
+        <v>-16.3571</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9101000000000008</v>
+        <v>1.6206</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2983</v>
+        <v>0.5851000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>6.208600000000001</v>
+        <v>1.036100000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.7026</v>
+        <v>-0.3642999999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.8633</v>
+        <v>1.1597</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.8392</v>
+        <v>-1.5246</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6367</v>
+        <v>3.9388</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0198</v>
+        <v>4.8721</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.656700000000001</v>
+        <v>-0.9330999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.0657</v>
+        <v>-4.303</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.8834</v>
+        <v>-3.712</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8174000000000003</v>
+        <v>-0.5914</v>
       </c>
       <c r="P13" t="n">
-        <v>12.9294</v>
+        <v>0.2275999999999996</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.1054</v>
+        <v>-14.1133</v>
       </c>
       <c r="R13" t="n">
-        <v>29.0347</v>
+        <v>14.3409</v>
       </c>
       <c r="S13" t="n">
-        <v>6.8786</v>
+        <v>8.2799</v>
       </c>
       <c r="T13" t="n">
-        <v>6.015700000000001</v>
+        <v>7.619000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8625000000000004</v>
+        <v>0.6607999999999997</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.1951</v>
+        <v>-6.522</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4278</v>
+        <v>3.1405</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.6228</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3668000000000005</v>
+        <v>0.6613000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6475</v>
+        <v>0.3426</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2806</v>
+        <v>0.3186999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1130000000000004</v>
+        <v>3.659</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9928000000000001</v>
+        <v>-0.3213999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1059</v>
+        <v>3.9804</v>
       </c>
       <c r="J14" t="n">
-        <v>2.913199999999999</v>
+        <v>4.728899999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>3.756</v>
+        <v>0.08200000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8424999999999998</v>
+        <v>4.6469</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0266</v>
+        <v>-1.0699</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.7632</v>
+        <v>-0.4033999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2629999999999998</v>
+        <v>-0.6664999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9072999999999997</v>
+        <v>0.4554000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.3002</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2075</v>
+        <v>3.8698</v>
       </c>
       <c r="S14" t="n">
-        <v>6.3535</v>
+        <v>-1.8186</v>
       </c>
       <c r="T14" t="n">
-        <v>5.6556</v>
+        <v>-1.2873</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6975</v>
+        <v>-0.5313</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.7809</v>
+        <v>-1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3784</v>
+        <v>0.3156</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.1593</v>
+        <v>-1.9498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. IROEGBU</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0483</v>
+        <v>-0.2455000000000003</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2817</v>
+        <v>-14.6537</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2333</v>
+        <v>14.4079</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8829</v>
+        <v>8.417000000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5326</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4154</v>
+        <v>-1.569800000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0084</v>
+        <v>19.7343</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5643</v>
+        <v>14.8354</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5727</v>
+        <v>4.8987</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1255</v>
+        <v>-11.3169</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0318</v>
+        <v>-4.8483</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>-6.4688</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-1.137799999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-45.5268</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>44.3883</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0974</v>
+        <v>-13.0433</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1391</v>
+        <v>-7.6416</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0417</v>
+        <v>-5.402</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>5.5189</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>18.7801</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-13.2614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>I. IROEGBU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.399299999999998</v>
+        <v>-2.0613</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.1233</v>
+        <v>-2.302</v>
       </c>
       <c r="F16" t="n">
-        <v>14.7237</v>
+        <v>0.2407</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.460999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0989</v>
+        <v>0.526</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.560300000000001</v>
+        <v>-1.4214</v>
       </c>
       <c r="J16" t="n">
-        <v>8.184799999999999</v>
+        <v>-1.0245</v>
       </c>
       <c r="K16" t="n">
-        <v>5.635</v>
+        <v>0.5548</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5498</v>
+        <v>-1.5793</v>
       </c>
       <c r="M16" t="n">
-        <v>-10.6459</v>
+        <v>0.129</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.5361</v>
+        <v>-0.0289</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.1099</v>
+        <v>0.1579</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.7219</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-40.8302</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>38.1078</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.6572</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.725</v>
+        <v>-0.1394</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.9325</v>
+        <v>0.0418</v>
       </c>
       <c r="V16" t="n">
-        <v>11.4409</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>20.2468</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.806100000000001</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,148 +1732,226 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.9308</v>
+        <v>-2.204000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5621</v>
+        <v>-12.4066</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3687</v>
+        <v>10.2027</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.8142</v>
+        <v>1.7565</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.525500000000001</v>
+        <v>-4.0002</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.2887</v>
+        <v>5.756900000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.3578</v>
+        <v>10.0917</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5979</v>
+        <v>3.840200000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7597</v>
+        <v>6.251299999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.4564</v>
+        <v>-8.335100000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9276</v>
+        <v>-7.8406</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.529</v>
+        <v>-0.4944000000000002</v>
       </c>
       <c r="P17" t="n">
-        <v>5.897699999999999</v>
+        <v>5.9185</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.2172</v>
+        <v>-22.9909</v>
       </c>
       <c r="R17" t="n">
-        <v>11.1149</v>
+        <v>28.9092</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6383</v>
+        <v>-1.4936</v>
       </c>
       <c r="T17" t="n">
-        <v>3.7594</v>
+        <v>-1.8886</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8789</v>
+        <v>0.3953000000000002</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.6526</v>
+        <v>-8.385400000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>2.3814</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.906</v>
+        <v>-10.7667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>I. NOGUES</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Valencia Basket</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-7.2758</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-5.734999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.541199999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-9.2258</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-2.8968</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-6.3291</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.8603</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-2.0273</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-7.3659</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.0639</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-4.302</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8.194800000000001</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-7.7395</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15.9344</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.4887</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4596</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.0294</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-9.7339</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4051</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-11.1388</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Valencia Basket</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" t="n">
-        <v>327.62</v>
-      </c>
-      <c r="E18" t="n">
-        <v>204.9676</v>
-      </c>
-      <c r="F18" t="n">
-        <v>122.6531</v>
-      </c>
-      <c r="G18" t="n">
-        <v>165.95</v>
-      </c>
-      <c r="H18" t="n">
-        <v>59.7968</v>
-      </c>
-      <c r="I18" t="n">
-        <v>106.1528</v>
-      </c>
-      <c r="J18" t="n">
-        <v>326.1901</v>
-      </c>
-      <c r="K18" t="n">
-        <v>158.7947</v>
-      </c>
-      <c r="L18" t="n">
-        <v>167.3959</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-160.2399</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-98.9975</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-61.2431</v>
-      </c>
-      <c r="P18" t="n">
-        <v>51.0374</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-382.2157</v>
-      </c>
-      <c r="R18" t="n">
-        <v>433.2515</v>
-      </c>
-      <c r="S18" t="n">
-        <v>93.72669999999999</v>
-      </c>
-      <c r="T18" t="n">
-        <v>85.09649999999999</v>
-      </c>
-      <c r="U18" t="n">
-        <v>8.629700000000003</v>
-      </c>
-      <c r="V18" t="n">
-        <v>16.9068</v>
-      </c>
-      <c r="W18" t="n">
-        <v>175.8942</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-158.988</v>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="n">
+        <v>385.1138999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>240.8989</v>
+      </c>
+      <c r="F19" t="n">
+        <v>144.2152</v>
+      </c>
+      <c r="G19" t="n">
+        <v>212.6374</v>
+      </c>
+      <c r="H19" t="n">
+        <v>102.1076</v>
+      </c>
+      <c r="I19" t="n">
+        <v>110.5305</v>
+      </c>
+      <c r="J19" t="n">
+        <v>411.8248</v>
+      </c>
+      <c r="K19" t="n">
+        <v>224.8575</v>
+      </c>
+      <c r="L19" t="n">
+        <v>186.9681</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-199.1876</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-122.7497</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-76.43700000000001</v>
+      </c>
+      <c r="P19" t="n">
+        <v>63.73779999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-464.3717</v>
+      </c>
+      <c r="R19" t="n">
+        <v>528.1087</v>
+      </c>
+      <c r="S19" t="n">
+        <v>103.3176</v>
+      </c>
+      <c r="T19" t="n">
+        <v>90.66980000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>12.6468</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.423499999999997</v>
+      </c>
+      <c r="W19" t="n">
+        <v>202.7741</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-197.3501</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -565,13 +565,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>90.084</v>
+        <v>73.0055</v>
       </c>
       <c r="E2" t="n">
-        <v>57.4974</v>
+        <v>46.9352</v>
       </c>
       <c r="F2" t="n">
-        <v>32.5869</v>
+        <v>26.0704</v>
       </c>
       <c r="G2" t="n">
         <v>45.8065</v>
@@ -610,13 +610,13 @@
         <v>50.7621</v>
       </c>
       <c r="S2" t="n">
-        <v>37.945</v>
+        <v>20.8664</v>
       </c>
       <c r="T2" t="n">
-        <v>25.4025</v>
+        <v>14.8401</v>
       </c>
       <c r="U2" t="n">
-        <v>12.5419</v>
+        <v>6.0259</v>
       </c>
       <c r="V2" t="n">
         <v>10.6579</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>53.52</v>
+        <v>67.4032</v>
       </c>
       <c r="E3" t="n">
-        <v>36.8411</v>
+        <v>50.3939</v>
       </c>
       <c r="F3" t="n">
-        <v>16.6792</v>
+        <v>17.0092</v>
       </c>
       <c r="G3" t="n">
-        <v>15.5093</v>
+        <v>32.8167</v>
       </c>
       <c r="H3" t="n">
-        <v>10.0393</v>
+        <v>-1.325300000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.469799999999999</v>
+        <v>34.1421</v>
       </c>
       <c r="J3" t="n">
-        <v>29.2054</v>
+        <v>53.9205</v>
       </c>
       <c r="K3" t="n">
-        <v>16.731</v>
+        <v>14.3035</v>
       </c>
       <c r="L3" t="n">
-        <v>12.4742</v>
+        <v>39.6167</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.6963</v>
+        <v>-21.1035</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.6917</v>
+        <v>-15.6289</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.004300000000001</v>
+        <v>-5.4747</v>
       </c>
       <c r="P3" t="n">
-        <v>17.5276</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q3" t="n">
-        <v>-18.6662</v>
+        <v>-42.7948</v>
       </c>
       <c r="R3" t="n">
-        <v>36.1935</v>
+        <v>40.5188</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1071</v>
+        <v>6.5005</v>
       </c>
       <c r="T3" t="n">
-        <v>26.2421</v>
+        <v>6.6408</v>
       </c>
       <c r="U3" t="n">
-        <v>5.8656</v>
+        <v>-0.1406000000000002</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.6239</v>
+        <v>30.3622</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05979999999999969</v>
+        <v>32.6275</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.6838</v>
+        <v>-2.2654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>51.917</v>
+        <v>45.3261</v>
       </c>
       <c r="E4" t="n">
-        <v>37.0788</v>
+        <v>33.8184</v>
       </c>
       <c r="F4" t="n">
-        <v>14.8382</v>
+        <v>11.5078</v>
       </c>
       <c r="G4" t="n">
-        <v>32.8167</v>
+        <v>31.0144</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.325300000000001</v>
+        <v>2.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>34.1421</v>
+        <v>28.9356</v>
       </c>
       <c r="J4" t="n">
-        <v>53.9205</v>
+        <v>45.1506</v>
       </c>
       <c r="K4" t="n">
-        <v>14.3035</v>
+        <v>11.7912</v>
       </c>
       <c r="L4" t="n">
-        <v>39.6167</v>
+        <v>33.3597</v>
       </c>
       <c r="M4" t="n">
-        <v>-21.1035</v>
+        <v>-14.1366</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.6289</v>
+        <v>-9.712400000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.4747</v>
+        <v>-4.4239</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2764</v>
+        <v>-11.3815</v>
       </c>
       <c r="Q4" t="n">
-        <v>-42.7948</v>
+        <v>-54.6319</v>
       </c>
       <c r="R4" t="n">
-        <v>40.5188</v>
+        <v>43.2501</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.9855</v>
+        <v>11.5151</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.674399999999999</v>
+        <v>10.5852</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.3114</v>
+        <v>0.9302999999999998</v>
       </c>
       <c r="V4" t="n">
-        <v>30.3622</v>
+        <v>14.178</v>
       </c>
       <c r="W4" t="n">
-        <v>32.6275</v>
+        <v>32.7142</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2654</v>
+        <v>-18.5359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>42.927</v>
+        <v>41.8563</v>
       </c>
       <c r="E5" t="n">
-        <v>34.689</v>
+        <v>36.3868</v>
       </c>
       <c r="F5" t="n">
-        <v>8.237800000000002</v>
+        <v>5.4695</v>
       </c>
       <c r="G5" t="n">
-        <v>31.0144</v>
+        <v>33.8445</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0785</v>
+        <v>12.1535</v>
       </c>
       <c r="I5" t="n">
-        <v>28.9356</v>
+        <v>21.6906</v>
       </c>
       <c r="J5" t="n">
-        <v>45.1506</v>
+        <v>54.5956</v>
       </c>
       <c r="K5" t="n">
-        <v>11.7912</v>
+        <v>24.1242</v>
       </c>
       <c r="L5" t="n">
-        <v>33.3597</v>
+        <v>30.472</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.1366</v>
+        <v>-20.7515</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.712400000000001</v>
+        <v>-11.9703</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.4239</v>
+        <v>-8.781000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.3815</v>
+        <v>-2.2761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-54.6319</v>
+        <v>-44.3884</v>
       </c>
       <c r="R5" t="n">
-        <v>43.2501</v>
+        <v>42.1121</v>
       </c>
       <c r="S5" t="n">
-        <v>9.116</v>
+        <v>7.9025</v>
       </c>
       <c r="T5" t="n">
-        <v>11.4556</v>
+        <v>6.4675</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.3398</v>
+        <v>1.4352</v>
       </c>
       <c r="V5" t="n">
-        <v>14.178</v>
+        <v>2.3856</v>
       </c>
       <c r="W5" t="n">
-        <v>32.7142</v>
+        <v>19.7118</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.5359</v>
+        <v>-17.3262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7805</v>
+        <v>41.1947</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9203</v>
+        <v>24.1957</v>
       </c>
       <c r="F6" t="n">
-        <v>13.86</v>
+        <v>16.9992</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5379</v>
+        <v>15.5093</v>
       </c>
       <c r="H6" t="n">
-        <v>9.8659</v>
+        <v>10.0393</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3282000000000003</v>
+        <v>5.469799999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>24.6113</v>
+        <v>29.2054</v>
       </c>
       <c r="K6" t="n">
-        <v>16.0019</v>
+        <v>16.731</v>
       </c>
       <c r="L6" t="n">
-        <v>8.609500000000001</v>
+        <v>12.4742</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.0734</v>
+        <v>-13.6963</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.1358</v>
+        <v>-6.6917</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.9376</v>
+        <v>-7.004300000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>21.8527</v>
+        <v>17.5276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-19.3491</v>
+        <v>-18.6662</v>
       </c>
       <c r="R6" t="n">
-        <v>41.2017</v>
+        <v>36.1935</v>
       </c>
       <c r="S6" t="n">
-        <v>25.209</v>
+        <v>19.7821</v>
       </c>
       <c r="T6" t="n">
-        <v>17.0473</v>
+        <v>13.5964</v>
       </c>
       <c r="U6" t="n">
-        <v>8.161300000000001</v>
+        <v>6.1856</v>
       </c>
       <c r="V6" t="n">
-        <v>-17.8185</v>
+        <v>-11.6239</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6108</v>
+        <v>0.05979999999999969</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.4293</v>
+        <v>-11.6838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>28.8635</v>
+        <v>32.5847</v>
       </c>
       <c r="E7" t="n">
-        <v>27.5724</v>
+        <v>19.7513</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2912</v>
+        <v>12.8338</v>
       </c>
       <c r="G7" t="n">
-        <v>33.8445</v>
+        <v>9.5379</v>
       </c>
       <c r="H7" t="n">
-        <v>12.1535</v>
+        <v>9.8659</v>
       </c>
       <c r="I7" t="n">
-        <v>21.6906</v>
+        <v>-0.3282000000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>54.5956</v>
+        <v>24.6113</v>
       </c>
       <c r="K7" t="n">
-        <v>24.1242</v>
+        <v>16.0019</v>
       </c>
       <c r="L7" t="n">
-        <v>30.472</v>
+        <v>8.609500000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-20.7515</v>
+        <v>-15.0734</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.9703</v>
+        <v>-6.1358</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.781000000000001</v>
+        <v>-8.9376</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2761</v>
+        <v>21.8527</v>
       </c>
       <c r="Q7" t="n">
-        <v>-44.3884</v>
+        <v>-19.3491</v>
       </c>
       <c r="R7" t="n">
-        <v>42.1121</v>
+        <v>41.2017</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.0898</v>
+        <v>19.0132</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.3471</v>
+        <v>11.8784</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.7428</v>
+        <v>7.1347</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3856</v>
+        <v>-17.8185</v>
       </c>
       <c r="W7" t="n">
-        <v>19.7118</v>
+        <v>2.6108</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.3262</v>
+        <v>-20.4293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>24.1084</v>
+        <v>31.7624</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2023</v>
+        <v>28.1859</v>
       </c>
       <c r="F8" t="n">
-        <v>20.906</v>
+        <v>3.5762</v>
       </c>
       <c r="G8" t="n">
-        <v>-9.3499</v>
+        <v>19.104</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9197</v>
+        <v>11.4071</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.4299</v>
+        <v>7.696999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.656199999999999</v>
+        <v>35.3609</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.455</v>
+        <v>16.6968</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.201300000000001</v>
+        <v>18.6645</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.6937</v>
+        <v>-16.2568</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4647</v>
+        <v>-5.2895</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2284</v>
+        <v>-10.9674</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5042</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.487</v>
+        <v>-29.8197</v>
       </c>
       <c r="R8" t="n">
-        <v>22.991</v>
+        <v>36.6489</v>
       </c>
       <c r="S8" t="n">
-        <v>17.2495</v>
+        <v>5.0776</v>
       </c>
       <c r="T8" t="n">
-        <v>10.6697</v>
+        <v>5.0407</v>
       </c>
       <c r="U8" t="n">
-        <v>6.579400000000001</v>
+        <v>0.03729999999999989</v>
       </c>
       <c r="V8" t="n">
-        <v>13.7048</v>
+        <v>0.7512999999999996</v>
       </c>
       <c r="W8" t="n">
-        <v>17.6756</v>
+        <v>17.6043</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.970899999999999</v>
+        <v>-16.8529</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>20.3726</v>
+        <v>24.1329</v>
       </c>
       <c r="E9" t="n">
-        <v>6.481199999999999</v>
+        <v>11.2334</v>
       </c>
       <c r="F9" t="n">
-        <v>13.8912</v>
+        <v>12.8994</v>
       </c>
       <c r="G9" t="n">
         <v>33.0059</v>
@@ -1156,13 +1156,13 @@
         <v>39.6082</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4511999999999997</v>
+        <v>4.2115</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.7677</v>
+        <v>1.9842</v>
       </c>
       <c r="U9" t="n">
-        <v>3.219</v>
+        <v>2.2272</v>
       </c>
       <c r="V9" t="n">
         <v>-5.8003</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>20.3436</v>
+        <v>22.4398</v>
       </c>
       <c r="E10" t="n">
-        <v>23.4898</v>
+        <v>25.1012</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.146</v>
+        <v>-2.6611</v>
       </c>
       <c r="G10" t="n">
-        <v>19.104</v>
+        <v>5.2288</v>
       </c>
       <c r="H10" t="n">
-        <v>11.4071</v>
+        <v>10.0594</v>
       </c>
       <c r="I10" t="n">
-        <v>7.696999999999999</v>
+        <v>-4.8303</v>
       </c>
       <c r="J10" t="n">
-        <v>35.3609</v>
+        <v>21.0494</v>
       </c>
       <c r="K10" t="n">
-        <v>16.6968</v>
+        <v>19.7736</v>
       </c>
       <c r="L10" t="n">
-        <v>18.6645</v>
+        <v>1.2758</v>
       </c>
       <c r="M10" t="n">
-        <v>-16.2568</v>
+        <v>-15.8204</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.2895</v>
+        <v>-9.7143</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.9674</v>
+        <v>-6.106299999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>6.829000000000001</v>
+        <v>15.7067</v>
       </c>
       <c r="Q10" t="n">
-        <v>-29.8197</v>
+        <v>-21.1699</v>
       </c>
       <c r="R10" t="n">
-        <v>36.6489</v>
+        <v>36.8768</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.3409</v>
+        <v>2.1578</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3442999999999998</v>
+        <v>6.1825</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.6852</v>
+        <v>-4.0244</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7512999999999996</v>
+        <v>-0.6536999999999997</v>
       </c>
       <c r="W10" t="n">
-        <v>17.6043</v>
+        <v>19.039</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.8529</v>
+        <v>-19.6927</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>20.1007</v>
+        <v>17.2494</v>
       </c>
       <c r="E11" t="n">
-        <v>24.7805</v>
+        <v>-3.1639</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6797</v>
+        <v>20.413</v>
       </c>
       <c r="G11" t="n">
-        <v>5.2288</v>
+        <v>8.417000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>10.0594</v>
+        <v>9.987400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.8303</v>
+        <v>-1.569800000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>21.0494</v>
+        <v>19.7343</v>
       </c>
       <c r="K11" t="n">
-        <v>19.7736</v>
+        <v>14.8354</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2758</v>
+        <v>4.8987</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.8204</v>
+        <v>-11.3169</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.7143</v>
+        <v>-4.8483</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.106299999999999</v>
+        <v>-6.4688</v>
       </c>
       <c r="P11" t="n">
-        <v>15.7067</v>
+        <v>-1.137799999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-21.1699</v>
+        <v>-45.5268</v>
       </c>
       <c r="R11" t="n">
-        <v>36.8768</v>
+        <v>44.3883</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.181</v>
+        <v>4.4518</v>
       </c>
       <c r="T11" t="n">
-        <v>5.862000000000001</v>
+        <v>3.8484</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.0428</v>
+        <v>0.6031999999999997</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6536999999999997</v>
+        <v>5.5189</v>
       </c>
       <c r="W11" t="n">
-        <v>19.039</v>
+        <v>18.7801</v>
       </c>
       <c r="X11" t="n">
-        <v>-19.6927</v>
+        <v>-13.2614</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>3.601300000000001</v>
+        <v>16.5288</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.484300000000001</v>
+        <v>-1.493399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>5.0855</v>
+        <v>18.0224</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.2277</v>
+        <v>-9.3499</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.1522</v>
+        <v>-3.9197</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0754</v>
+        <v>-5.4299</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8123</v>
+        <v>-4.656199999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1184</v>
+        <v>-1.455</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.306500000000001</v>
+        <v>-3.201300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.040099999999999</v>
+        <v>-4.6937</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.2709</v>
+        <v>-2.4647</v>
       </c>
       <c r="O12" t="n">
-        <v>1.231</v>
+        <v>-2.2284</v>
       </c>
       <c r="P12" t="n">
-        <v>14.1132</v>
+        <v>2.5042</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.1622</v>
+        <v>-20.487</v>
       </c>
       <c r="R12" t="n">
-        <v>30.2753</v>
+        <v>22.991</v>
       </c>
       <c r="S12" t="n">
-        <v>6.5215</v>
+        <v>9.67</v>
       </c>
       <c r="T12" t="n">
-        <v>6.313800000000001</v>
+        <v>5.974</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2075999999999998</v>
+        <v>3.6962</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.8055</v>
+        <v>13.7048</v>
       </c>
       <c r="W12" t="n">
-        <v>6.5518</v>
+        <v>17.6756</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.3571</v>
+        <v>-3.970899999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6206</v>
+        <v>7.808</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5851000000000002</v>
+        <v>0.9617999999999993</v>
       </c>
       <c r="F13" t="n">
-        <v>1.036100000000001</v>
+        <v>6.846400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3642999999999998</v>
+        <v>-7.2277</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1597</v>
+        <v>-5.1522</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5246</v>
+        <v>-2.0754</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9388</v>
+        <v>1.8123</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8721</v>
+        <v>5.1184</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9330999999999998</v>
+        <v>-3.306500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.303</v>
+        <v>-9.040099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.712</v>
+        <v>-10.2709</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5914</v>
+        <v>1.231</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2275999999999996</v>
+        <v>14.1132</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.1133</v>
+        <v>-16.1622</v>
       </c>
       <c r="R13" t="n">
-        <v>14.3409</v>
+        <v>30.2753</v>
       </c>
       <c r="S13" t="n">
-        <v>8.2799</v>
+        <v>10.7279</v>
       </c>
       <c r="T13" t="n">
-        <v>7.619000000000001</v>
+        <v>8.7597</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6607999999999997</v>
+        <v>1.9683</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.522</v>
+        <v>-9.8055</v>
       </c>
       <c r="W13" t="n">
-        <v>3.1405</v>
+        <v>6.5518</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.6624</v>
+        <v>-16.3571</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6613000000000002</v>
+        <v>2.2118</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3426</v>
+        <v>1.548</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3186999999999999</v>
+        <v>0.6637</v>
       </c>
       <c r="G14" t="n">
         <v>3.659</v>
@@ -1546,13 +1546,13 @@
         <v>3.8698</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8186</v>
+        <v>-0.2682</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2873</v>
+        <v>-0.08189999999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5313</v>
+        <v>-0.1864</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6342</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2455000000000003</v>
+        <v>1.633900000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.6537</v>
+        <v>-9.173599999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>14.4079</v>
+        <v>10.8074</v>
       </c>
       <c r="G15" t="n">
-        <v>8.417000000000002</v>
+        <v>1.7565</v>
       </c>
       <c r="H15" t="n">
-        <v>9.987400000000001</v>
+        <v>-4.0002</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.569800000000001</v>
+        <v>5.756900000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>19.7343</v>
+        <v>10.0917</v>
       </c>
       <c r="K15" t="n">
-        <v>14.8354</v>
+        <v>3.840200000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8987</v>
+        <v>6.251299999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-11.3169</v>
+        <v>-8.335100000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.8483</v>
+        <v>-7.8406</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.4688</v>
+        <v>-0.4944000000000002</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.137799999999999</v>
+        <v>5.9185</v>
       </c>
       <c r="Q15" t="n">
-        <v>-45.5268</v>
+        <v>-22.9909</v>
       </c>
       <c r="R15" t="n">
-        <v>44.3883</v>
+        <v>28.9092</v>
       </c>
       <c r="S15" t="n">
-        <v>-13.0433</v>
+        <v>2.3446</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.6416</v>
+        <v>1.3443</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.402</v>
+        <v>1.0003</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5189</v>
+        <v>-8.385400000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>18.7801</v>
+        <v>2.3814</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.2614</v>
+        <v>-10.7667</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0613</v>
+        <v>-1.7617</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.302</v>
+        <v>-2.0651</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2407</v>
+        <v>0.3035</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8954</v>
@@ -1702,13 +1702,13 @@
         <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.09760000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1394</v>
+        <v>0.0975</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0418</v>
+        <v>0.1046</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1578</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.204000000000001</v>
+        <v>-2.642000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.4066</v>
+        <v>-3.992399999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>10.2027</v>
+        <v>1.3507</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7565</v>
+        <v>-0.3642999999999998</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.0002</v>
+        <v>1.1597</v>
       </c>
       <c r="I17" t="n">
-        <v>5.756900000000001</v>
+        <v>-1.5246</v>
       </c>
       <c r="J17" t="n">
-        <v>10.0917</v>
+        <v>3.9388</v>
       </c>
       <c r="K17" t="n">
-        <v>3.840200000000001</v>
+        <v>4.8721</v>
       </c>
       <c r="L17" t="n">
-        <v>6.251299999999999</v>
+        <v>-0.9330999999999998</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.335100000000001</v>
+        <v>-4.303</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.8406</v>
+        <v>-3.712</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4944000000000002</v>
+        <v>-0.5914</v>
       </c>
       <c r="P17" t="n">
-        <v>5.9185</v>
+        <v>0.2275999999999996</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.9909</v>
+        <v>-14.1133</v>
       </c>
       <c r="R17" t="n">
-        <v>28.9092</v>
+        <v>14.3409</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4936</v>
+        <v>4.016999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.8886</v>
+        <v>3.0414</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3953000000000002</v>
+        <v>0.9754999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-8.385400000000001</v>
+        <v>-6.522</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3814</v>
+        <v>3.1405</v>
       </c>
       <c r="X17" t="n">
-        <v>-10.7667</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.2758</v>
+        <v>-7.1101</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.734999999999999</v>
+        <v>-5.0589</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.541199999999999</v>
+        <v>-2.0513</v>
       </c>
       <c r="G18" t="n">
         <v>-9.2258</v>
@@ -1858,13 +1858,13 @@
         <v>15.9344</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4887</v>
+        <v>3.6549</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4596</v>
+        <v>3.1357</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0294</v>
+        <v>0.5192</v>
       </c>
       <c r="V18" t="n">
         <v>-9.7339</v>
@@ -1891,13 +1891,13 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>385.1138999999999</v>
+        <v>413.6237</v>
       </c>
       <c r="E19" t="n">
-        <v>240.8989</v>
+        <v>253.5643</v>
       </c>
       <c r="F19" t="n">
-        <v>144.2152</v>
+        <v>160.0602</v>
       </c>
       <c r="G19" t="n">
         <v>212.6374</v>
@@ -1927,25 +1927,25 @@
         <v>-76.43700000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>63.73779999999999</v>
+        <v>63.7378</v>
       </c>
       <c r="Q19" t="n">
-        <v>-464.3717</v>
+        <v>-464.3717000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>528.1087</v>
+        <v>528.1086999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>103.3176</v>
+        <v>131.8267</v>
       </c>
       <c r="T19" t="n">
-        <v>90.66980000000001</v>
+        <v>103.3349</v>
       </c>
       <c r="U19" t="n">
-        <v>12.6468</v>
+        <v>28.4921</v>
       </c>
       <c r="V19" t="n">
-        <v>5.423499999999997</v>
+        <v>5.423499999999988</v>
       </c>
       <c r="W19" t="n">
         <v>202.7741</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Valencia Basket.xlsx
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
         <v>413.6237</v>
